--- a/public/template/elder_infor_upload_template.xlsx
+++ b/public/template/elder_infor_upload_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630"/>
+    <workbookView windowWidth="17880" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,57 +27,124 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>姓名</t>
+  </si>
   <si>
     <t>身份证号</t>
   </si>
   <si>
-    <t>姓名</t>
+    <t>手机号</t>
+  </si>
+  <si>
+    <t>当前状态</t>
+  </si>
+  <si>
+    <t>原住地-省份</t>
+  </si>
+  <si>
+    <t>原住地-城市</t>
+  </si>
+  <si>
+    <t>原住地-社区</t>
+  </si>
+  <si>
+    <t>迁入地-省份</t>
+  </si>
+  <si>
+    <t>迁入地-城市</t>
+  </si>
+  <si>
+    <t>迁入地-社区</t>
+  </si>
+  <si>
+    <t>迁入地详细住址</t>
+  </si>
+  <si>
+    <t>年龄</t>
   </si>
   <si>
     <t>性别</t>
   </si>
   <si>
-    <t>年龄</t>
-  </si>
-  <si>
-    <t>当前状态</t>
-  </si>
-  <si>
-    <t>手机号</t>
-  </si>
-  <si>
-    <t>原住地-省</t>
-  </si>
-  <si>
-    <t>原住地-市</t>
-  </si>
-  <si>
-    <t>原住地-社区</t>
-  </si>
-  <si>
-    <t>迁入地-省</t>
-  </si>
-  <si>
-    <t>迁入地-市</t>
-  </si>
-  <si>
-    <t>迁入地-社区</t>
-  </si>
-  <si>
-    <t>迁入地具体住址</t>
-  </si>
-  <si>
-    <t>异地医保状态</t>
+    <t>居住开始时间</t>
+  </si>
+  <si>
+    <t>居住结束时间</t>
+  </si>
+  <si>
+    <t>夫妻同住</t>
+  </si>
+  <si>
+    <t>配偶姓名</t>
+  </si>
+  <si>
+    <t>紧急联系人</t>
+  </si>
+  <si>
+    <t>紧急联系人关系</t>
+  </si>
+  <si>
+    <t>紧急联系人电话</t>
+  </si>
+  <si>
+    <t>健康状况</t>
+  </si>
+  <si>
+    <t>健康备注</t>
+  </si>
+  <si>
+    <t>异地医保</t>
+  </si>
+  <si>
+    <t>才艺特长/兴趣爱好</t>
+  </si>
+  <si>
+    <t>志愿等级</t>
+  </si>
+  <si>
+    <t>上传时：删去此行</t>
   </si>
   <si>
     <t>待抵达/居住中/已返乡</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>注意</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：原住地及迁入地省份、城市、社区需按规定标准名称填入</t>
+    </r>
+  </si>
+  <si>
+    <t>是/否</t>
+  </si>
+  <si>
+    <t>子女/朋友/配偶</t>
+  </si>
+  <si>
+    <t>完全自理/半自理</t>
+  </si>
+  <si>
     <t>已备案/未备案</t>
   </si>
   <si>
-    <t>示例说明(上传时删掉)</t>
+    <t>候鸟老年人才/候鸟老年志愿者/普通候鸟老人（非必填）</t>
   </si>
 </sst>
 </file>
@@ -90,7 +157,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +169,13 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -583,137 +657,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -724,6 +798,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1251,24 +1328,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="14.8181818181818" customWidth="1"/>
-    <col min="2" max="2" width="9.27272727272727" customWidth="1"/>
-    <col min="3" max="4" width="9.18181818181818" customWidth="1"/>
+    <col min="1" max="1" width="11.6363636363636" customWidth="1"/>
+    <col min="2" max="2" width="15.7272727272727" customWidth="1"/>
+    <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
+    <col min="4" max="4" width="20.8181818181818" customWidth="1"/>
     <col min="5" max="5" width="21.4545454545455" customWidth="1"/>
     <col min="6" max="6" width="19.8181818181818" customWidth="1"/>
     <col min="7" max="7" width="15.9090909090909" customWidth="1"/>
     <col min="8" max="8" width="15.1818181818182" customWidth="1"/>
     <col min="9" max="10" width="16.7272727272727" customWidth="1"/>
-    <col min="11" max="12" width="15.1818181818182" customWidth="1"/>
-    <col min="13" max="13" width="18.1818181818182" customWidth="1"/>
+    <col min="11" max="11" width="19.2727272727273" customWidth="1"/>
+    <col min="12" max="12" width="12.1818181818182" customWidth="1"/>
+    <col min="13" max="13" width="11.6363636363636" customWidth="1"/>
     <col min="14" max="14" width="17.1818181818182" customWidth="1"/>
     <col min="15" max="15" width="16.5454545454545" customWidth="1"/>
+    <col min="16" max="16" width="11.4545454545455" customWidth="1"/>
+    <col min="17" max="17" width="11.7272727272727" customWidth="1"/>
+    <col min="18" max="18" width="13.8181818181818" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="17.6363636363636" customWidth="1"/>
+    <col min="21" max="21" width="16.4545454545455" customWidth="1"/>
+    <col min="22" max="22" width="13.3636363636364" customWidth="1"/>
+    <col min="23" max="23" width="15.6363636363636" customWidth="1"/>
+    <col min="24" max="24" width="22.9090909090909" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:15">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1311,28 +1400,69 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" ht="15" spans="1:15">
-      <c r="A2" s="2"/>
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:25">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>16</v>
+      <c r="G2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
